--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2791,6 +2791,243 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124952743</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96979</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lid, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>335297</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6433669</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124952259</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lid, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>335178</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6433674</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -2793,10 +2793,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124952743</v>
+        <v>124952259</v>
       </c>
       <c r="B19" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2805,31 +2805,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2837,10 +2841,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>335297</v>
+        <v>335178</v>
       </c>
       <c r="R19" t="n">
-        <v>6433669</v>
+        <v>6433674</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2867,22 +2871,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2891,7 +2895,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2910,10 +2913,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124952259</v>
+        <v>124952743</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2922,35 +2925,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2958,10 +2957,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>335178</v>
+        <v>335297</v>
       </c>
       <c r="R20" t="n">
-        <v>6433674</v>
+        <v>6433669</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2988,22 +2987,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3012,6 +3011,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -2793,10 +2793,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124952259</v>
+        <v>124952743</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2805,35 +2805,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2841,10 +2837,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>335178</v>
+        <v>335297</v>
       </c>
       <c r="R19" t="n">
-        <v>6433674</v>
+        <v>6433669</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2871,22 +2867,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2895,6 +2891,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2913,10 +2910,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124952743</v>
+        <v>124952259</v>
       </c>
       <c r="B20" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2925,31 +2922,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2957,10 +2958,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>335297</v>
+        <v>335178</v>
       </c>
       <c r="R20" t="n">
-        <v>6433669</v>
+        <v>6433674</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2987,22 +2988,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3011,7 +3012,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -2793,10 +2793,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124952259</v>
+        <v>124952743</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>97147</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2805,35 +2805,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2841,10 +2837,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>335178</v>
+        <v>335297</v>
       </c>
       <c r="R19" t="n">
-        <v>6433674</v>
+        <v>6433669</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2871,22 +2867,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2895,6 +2891,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2913,10 +2910,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124952743</v>
+        <v>124952259</v>
       </c>
       <c r="B20" t="n">
-        <v>96979</v>
+        <v>57632</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2925,31 +2922,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2957,10 +2958,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>335297</v>
+        <v>335178</v>
       </c>
       <c r="R20" t="n">
-        <v>6433669</v>
+        <v>6433674</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2987,22 +2988,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3011,7 +3012,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -2793,10 +2793,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124952743</v>
+        <v>124952259</v>
       </c>
       <c r="B19" t="n">
-        <v>97147</v>
+        <v>57632</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2805,31 +2805,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2837,10 +2841,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>335297</v>
+        <v>335178</v>
       </c>
       <c r="R19" t="n">
-        <v>6433669</v>
+        <v>6433674</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2867,22 +2871,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2891,7 +2895,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2910,10 +2913,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124952259</v>
+        <v>124952743</v>
       </c>
       <c r="B20" t="n">
-        <v>57632</v>
+        <v>97147</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2922,35 +2925,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2958,10 +2957,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>335178</v>
+        <v>335297</v>
       </c>
       <c r="R20" t="n">
-        <v>6433674</v>
+        <v>6433669</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2988,22 +2987,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3012,6 +3011,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3018,6 +3018,232 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125854575</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lid, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>335238</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6433763</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125855127</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lid, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>335157</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6433709</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3244,6 +3244,1420 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126123835</v>
+      </c>
+      <c r="B23" t="n">
+        <v>96628</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lid pos8, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>335210</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6433711</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126123713</v>
+      </c>
+      <c r="B24" t="n">
+        <v>96628</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lid pos6, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>335247</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6433706</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126123480</v>
+      </c>
+      <c r="B25" t="n">
+        <v>95788</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>210</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lid pos2, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>335229</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6433701</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>protonemakuddar</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126123778</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96592</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>53</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lid pos7, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>335244</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6433710</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126123977</v>
+      </c>
+      <c r="B27" t="n">
+        <v>96628</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lid pos9, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>335210</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6433705</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>på samma klen låga som vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126123937</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96592</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>53</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lid pos9, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>335210</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6433705</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126123853</v>
+      </c>
+      <c r="B29" t="n">
+        <v>96592</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>53</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lid pos8, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>335210</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6433711</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126123596</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96592</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>53</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lid pos4, Vg</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>335325</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6433704</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>växte i rena bestånd och inspränd blan pigglummermossa på två tallstockar</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>klena</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Pinus sylvestris # klena</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126123411</v>
+      </c>
+      <c r="B31" t="n">
+        <v>95788</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>210</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lid pos1, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>335268</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6433671</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>protonemakuddar och ett kapselskaft</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126123654</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97019</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lid pos5, Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>335331</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6433713</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126123541</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97019</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lid pos3, Vg</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>335333</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6433701</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126123748</v>
+      </c>
+      <c r="B34" t="n">
+        <v>96592</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>53</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lid pos6, Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>335247</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6433706</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -3953,7 +3953,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126123853</v>
+        <v>126123596</v>
       </c>
       <c r="B29" t="n">
         <v>96592</v>
@@ -3992,14 +3992,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lid pos8, Vg</t>
+          <t>Lid pos4, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>335210</v>
+        <v>335325</v>
       </c>
       <c r="R29" t="n">
-        <v>6433711</v>
+        <v>6433704</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4034,6 +4034,11 @@
           <t>2025-06-21</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>växte i rena bestånd och inspränd blan pigglummermossa på två tallstockar</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4046,17 +4051,25 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>klena</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>2</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>2 substratenheter # Pinus sylvestris # klena</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4074,7 +4087,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126123596</v>
+        <v>126123853</v>
       </c>
       <c r="B30" t="n">
         <v>96592</v>
@@ -4113,14 +4126,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lid pos4, Vg</t>
+          <t>Lid pos8, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>335325</v>
+        <v>335210</v>
       </c>
       <c r="R30" t="n">
-        <v>6433704</v>
+        <v>6433711</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4155,11 +4168,6 @@
           <t>2025-06-21</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>växte i rena bestånd och inspränd blan pigglummermossa på två tallstockar</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4172,25 +4180,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>klena</t>
-        </is>
-      </c>
-      <c r="AN30" t="n">
-        <v>2</v>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>2 substratenheter # Pinus sylvestris # klena</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>125854575</v>
       </c>
       <c r="B21" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>125855127</v>
       </c>
       <c r="B22" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>126123835</v>
       </c>
       <c r="B23" t="n">
-        <v>96628</v>
+        <v>96630</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>126123713</v>
       </c>
       <c r="B24" t="n">
-        <v>96628</v>
+        <v>96630</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>126123480</v>
       </c>
       <c r="B25" t="n">
-        <v>95788</v>
+        <v>95790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>126123778</v>
       </c>
       <c r="B26" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>126123977</v>
       </c>
       <c r="B27" t="n">
-        <v>96628</v>
+        <v>96630</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>126123937</v>
       </c>
       <c r="B28" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>126123596</v>
       </c>
       <c r="B29" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>126123853</v>
       </c>
       <c r="B30" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>126123411</v>
       </c>
       <c r="B31" t="n">
-        <v>95788</v>
+        <v>95790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>126123654</v>
       </c>
       <c r="B32" t="n">
-        <v>97019</v>
+        <v>97021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>126123541</v>
       </c>
       <c r="B33" t="n">
-        <v>97019</v>
+        <v>97021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>126123748</v>
       </c>
       <c r="B34" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3249,7 +3249,7 @@
         <v>126123835</v>
       </c>
       <c r="B23" t="n">
-        <v>96630</v>
+        <v>96632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>126123713</v>
       </c>
       <c r="B24" t="n">
-        <v>96630</v>
+        <v>96632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>126123480</v>
       </c>
       <c r="B25" t="n">
-        <v>95790</v>
+        <v>95792</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>126123778</v>
       </c>
       <c r="B26" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3706,32 +3706,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126123977</v>
+        <v>126123937</v>
       </c>
       <c r="B27" t="n">
-        <v>96630</v>
+        <v>96596</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3785,11 +3785,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>på samma klen låga som vedtrappmossa</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3832,32 +3827,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126123937</v>
+        <v>126123977</v>
       </c>
       <c r="B28" t="n">
-        <v>96594</v>
+        <v>96632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3911,6 +3906,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>på samma klen låga som vedtrappmossa</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3956,7 +3956,7 @@
         <v>126123596</v>
       </c>
       <c r="B29" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>126123853</v>
       </c>
       <c r="B30" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>126123411</v>
       </c>
       <c r="B31" t="n">
-        <v>95790</v>
+        <v>95792</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>126123654</v>
       </c>
       <c r="B32" t="n">
-        <v>97021</v>
+        <v>97023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4432,49 +4432,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126123541</v>
+        <v>126123748</v>
       </c>
       <c r="B33" t="n">
-        <v>97021</v>
+        <v>96596</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2606</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lid pos3, Vg</t>
+          <t>Lid pos6, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>335333</v>
+        <v>335247</v>
       </c>
       <c r="R33" t="n">
-        <v>6433701</v>
+        <v>6433706</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4518,6 +4522,26 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4534,53 +4558,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126123748</v>
+        <v>126123541</v>
       </c>
       <c r="B34" t="n">
-        <v>96594</v>
+        <v>97023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>2606</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lid pos6, Vg</t>
+          <t>Lid pos3, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>335247</v>
+        <v>335333</v>
       </c>
       <c r="R34" t="n">
-        <v>6433706</v>
+        <v>6433701</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4625,26 +4645,6 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4657,6 +4657,368 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126254969</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lid, norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>335255</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6433695</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126255697</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lid, nor om, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>335233</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6433688</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126255375</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58367</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lid, norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>335280</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6433660</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>En adult och en juvenil. Inne i äldre tallskog med mycket blåbärsris. Udda plats för arten.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -3249,7 +3249,7 @@
         <v>126123835</v>
       </c>
       <c r="B23" t="n">
-        <v>96632</v>
+        <v>96634</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>126123713</v>
       </c>
       <c r="B24" t="n">
-        <v>96632</v>
+        <v>96634</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>126123480</v>
       </c>
       <c r="B25" t="n">
-        <v>95792</v>
+        <v>95794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>126123778</v>
       </c>
       <c r="B26" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3706,32 +3706,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126123937</v>
+        <v>126123977</v>
       </c>
       <c r="B27" t="n">
-        <v>96596</v>
+        <v>96634</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3785,6 +3785,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>på samma klen låga som vedtrappmossa</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3827,32 +3832,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126123977</v>
+        <v>126123937</v>
       </c>
       <c r="B28" t="n">
-        <v>96632</v>
+        <v>96598</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3906,11 +3911,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>på samma klen låga som vedtrappmossa</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3956,7 +3956,7 @@
         <v>126123596</v>
       </c>
       <c r="B29" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>126123853</v>
       </c>
       <c r="B30" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>126123411</v>
       </c>
       <c r="B31" t="n">
-        <v>95792</v>
+        <v>95794</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>126123654</v>
       </c>
       <c r="B32" t="n">
-        <v>97023</v>
+        <v>97025</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4432,53 +4432,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126123748</v>
+        <v>126123541</v>
       </c>
       <c r="B33" t="n">
-        <v>96596</v>
+        <v>97025</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>2606</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lid pos6, Vg</t>
+          <t>Lid pos3, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>335247</v>
+        <v>335333</v>
       </c>
       <c r="R33" t="n">
-        <v>6433706</v>
+        <v>6433701</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4522,26 +4518,6 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4558,49 +4534,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126123541</v>
+        <v>126123748</v>
       </c>
       <c r="B34" t="n">
-        <v>97023</v>
+        <v>96598</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2606</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lid pos3, Vg</t>
+          <t>Lid pos6, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>335333</v>
+        <v>335247</v>
       </c>
       <c r="R34" t="n">
-        <v>6433701</v>
+        <v>6433706</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4644,6 +4624,26 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>125854575</v>
       </c>
       <c r="B21" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>125855127</v>
       </c>
       <c r="B22" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>126123835</v>
       </c>
       <c r="B23" t="n">
-        <v>96634</v>
+        <v>96638</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>126123713</v>
       </c>
       <c r="B24" t="n">
-        <v>96634</v>
+        <v>96638</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>126123480</v>
       </c>
       <c r="B25" t="n">
-        <v>95794</v>
+        <v>95798</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>126123778</v>
       </c>
       <c r="B26" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3706,32 +3706,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126123977</v>
+        <v>126123937</v>
       </c>
       <c r="B27" t="n">
-        <v>96634</v>
+        <v>96602</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3785,11 +3785,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>på samma klen låga som vedtrappmossa</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3832,32 +3827,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126123937</v>
+        <v>126123977</v>
       </c>
       <c r="B28" t="n">
-        <v>96598</v>
+        <v>96638</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3911,6 +3906,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>på samma klen låga som vedtrappmossa</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3956,7 +3956,7 @@
         <v>126123596</v>
       </c>
       <c r="B29" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>126123853</v>
       </c>
       <c r="B30" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>126123411</v>
       </c>
       <c r="B31" t="n">
-        <v>95794</v>
+        <v>95798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>126123654</v>
       </c>
       <c r="B32" t="n">
-        <v>97025</v>
+        <v>97029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4432,49 +4432,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126123541</v>
+        <v>126123748</v>
       </c>
       <c r="B33" t="n">
-        <v>97025</v>
+        <v>96602</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2606</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lid pos3, Vg</t>
+          <t>Lid pos6, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>335333</v>
+        <v>335247</v>
       </c>
       <c r="R33" t="n">
-        <v>6433701</v>
+        <v>6433706</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4518,6 +4522,26 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4534,53 +4558,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126123748</v>
+        <v>126123541</v>
       </c>
       <c r="B34" t="n">
-        <v>96598</v>
+        <v>97029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>2606</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lid pos6, Vg</t>
+          <t>Lid pos3, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>335247</v>
+        <v>335333</v>
       </c>
       <c r="R34" t="n">
-        <v>6433706</v>
+        <v>6433701</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4624,26 +4644,6 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4663,7 +4663,7 @@
         <v>126254969</v>
       </c>
       <c r="B35" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>126255697</v>
       </c>
       <c r="B36" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>126255375</v>
       </c>
       <c r="B37" t="n">
-        <v>58367</v>
+        <v>58371</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -3249,7 +3249,7 @@
         <v>126123835</v>
       </c>
       <c r="B23" t="n">
-        <v>96638</v>
+        <v>96641</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>126123713</v>
       </c>
       <c r="B24" t="n">
-        <v>96638</v>
+        <v>96641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>126123480</v>
       </c>
       <c r="B25" t="n">
-        <v>95798</v>
+        <v>95801</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>126123778</v>
       </c>
       <c r="B26" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3706,32 +3706,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126123937</v>
+        <v>126123977</v>
       </c>
       <c r="B27" t="n">
-        <v>96602</v>
+        <v>96641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3785,6 +3785,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>på samma klen låga som vedtrappmossa</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3827,32 +3832,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126123977</v>
+        <v>126123937</v>
       </c>
       <c r="B28" t="n">
-        <v>96638</v>
+        <v>96605</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3906,11 +3911,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>på samma klen låga som vedtrappmossa</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3956,7 +3956,7 @@
         <v>126123596</v>
       </c>
       <c r="B29" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>126123853</v>
       </c>
       <c r="B30" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>126123411</v>
       </c>
       <c r="B31" t="n">
-        <v>95798</v>
+        <v>95801</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>126123654</v>
       </c>
       <c r="B32" t="n">
-        <v>97029</v>
+        <v>97032</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4432,53 +4432,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126123748</v>
+        <v>126123541</v>
       </c>
       <c r="B33" t="n">
-        <v>96602</v>
+        <v>97032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>2606</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lid pos6, Vg</t>
+          <t>Lid pos3, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>335247</v>
+        <v>335333</v>
       </c>
       <c r="R33" t="n">
-        <v>6433706</v>
+        <v>6433701</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4522,26 +4518,6 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4558,49 +4534,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126123541</v>
+        <v>126123748</v>
       </c>
       <c r="B34" t="n">
-        <v>97029</v>
+        <v>96605</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2606</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med groddkorn</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lid pos3, Vg</t>
+          <t>Lid pos6, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>335333</v>
+        <v>335247</v>
       </c>
       <c r="R34" t="n">
-        <v>6433701</v>
+        <v>6433706</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4644,6 +4624,26 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -3023,7 +3023,7 @@
         <v>125854575</v>
       </c>
       <c r="B21" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>125855127</v>
       </c>
       <c r="B22" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>126123835</v>
       </c>
       <c r="B23" t="n">
-        <v>96641</v>
+        <v>96650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>126123713</v>
       </c>
       <c r="B24" t="n">
-        <v>96641</v>
+        <v>96650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>126123480</v>
       </c>
       <c r="B25" t="n">
-        <v>95801</v>
+        <v>95810</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>126123778</v>
       </c>
       <c r="B26" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>126123977</v>
       </c>
       <c r="B27" t="n">
-        <v>96641</v>
+        <v>96650</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>126123937</v>
       </c>
       <c r="B28" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>126123596</v>
       </c>
       <c r="B29" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>126123853</v>
       </c>
       <c r="B30" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>126123411</v>
       </c>
       <c r="B31" t="n">
-        <v>95801</v>
+        <v>95810</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>126123654</v>
       </c>
       <c r="B32" t="n">
-        <v>97032</v>
+        <v>97041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>126123541</v>
       </c>
       <c r="B33" t="n">
-        <v>97032</v>
+        <v>97041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>126123748</v>
       </c>
       <c r="B34" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>126254969</v>
       </c>
       <c r="B35" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>126255697</v>
       </c>
       <c r="B36" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>126255375</v>
       </c>
       <c r="B37" t="n">
-        <v>58371</v>
+        <v>58374</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -3835,7 +3835,7 @@
         <v>126123937</v>
       </c>
       <c r="B28" t="n">
-        <v>96614</v>
+        <v>96689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -3835,7 +3835,7 @@
         <v>126123937</v>
       </c>
       <c r="B28" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -3835,7 +3835,7 @@
         <v>126123937</v>
       </c>
       <c r="B28" t="n">
-        <v>96695</v>
+        <v>96696</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -3835,7 +3835,7 @@
         <v>126123937</v>
       </c>
       <c r="B28" t="n">
-        <v>96696</v>
+        <v>96700</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -3835,7 +3835,7 @@
         <v>126123937</v>
       </c>
       <c r="B28" t="n">
-        <v>96700</v>
+        <v>96702</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -3835,7 +3835,7 @@
         <v>126123937</v>
       </c>
       <c r="B28" t="n">
-        <v>96702</v>
+        <v>96689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 36325-2023 artfynd.xlsx
+++ b/artfynd/A 36325-2023 artfynd.xlsx
@@ -3835,7 +3835,7 @@
         <v>126123937</v>
       </c>
       <c r="B28" t="n">
-        <v>96689</v>
+        <v>96702</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
